--- a/public/templates/题目导入模板.xlsx
+++ b/public/templates/题目导入模板.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="30240" windowHeight="13100"/>
   </bookViews>
   <sheets>
     <sheet name="题目导入模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>项目代码</t>
   </si>
@@ -60,7 +60,7 @@
     <t>考试人员类型</t>
   </si>
   <si>
-    <t>AQGL</t>
+    <t>A</t>
   </si>
   <si>
     <t>法规知识</t>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>答案D</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>单选题</t>
@@ -732,10 +729,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1125,16 +1122,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="25" customHeight="1" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="10.2890625" defaultRowHeight="25" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="13.7142857142857" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.7142857142857" style="2" customWidth="1"/>
-    <col min="3" max="3" width="70.7142857142857" style="2" customWidth="1"/>
-    <col min="4" max="7" width="15.7142857142857" style="2" customWidth="1"/>
-    <col min="8" max="8" width="35.7142857142857" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.5714285714286" style="3" customWidth="1"/>
-    <col min="10" max="10" width="29.1428571428571" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="10.2857142857143" style="2"/>
+    <col min="1" max="1" width="13.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="70.7109375" style="2" customWidth="1"/>
+    <col min="4" max="7" width="15.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="10.2890625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="40" customHeight="1" spans="1:10">
@@ -1162,59 +1159,59 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 J1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:J1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>"单选题,判断题,多选题"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>"作业人员,检验人员"</formula1>
+      <formula1>"作业人员"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 B2:H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>